--- a/Patient_History.xlsx
+++ b/Patient_History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,16 @@
           <t>prediction_date</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>doctor_name</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -458,7 +468,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -467,7 +477,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Common Cold</t>
+          <t>malaria</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -475,6 +485,8 @@
           <t>2026-07-22 09:48:52</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
           <t>2026-07-22 11:56:00</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -531,6 +545,8 @@
           <t>2026-07-22 12:04:52</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -559,6 +575,8 @@
           <t>2026-07-22 12:08:51</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -587,6 +605,8 @@
           <t>2026-07-22 12:14:56</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -615,6 +635,8 @@
           <t>2026-07-22 12:21:56</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -643,6 +665,8 @@
           <t>2026-07-22 12:26:14</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -671,6 +695,8 @@
           <t>2026-07-22 12:34:57</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -699,6 +725,8 @@
           <t>2026-07-22 12:40:32</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -727,6 +755,8 @@
           <t>2026-07-22 13:00:44</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -755,6 +785,8 @@
           <t>2026-07-22 13:02:01</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -783,6 +815,8 @@
           <t>2026-07-23 11:07:46</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -811,6 +845,8 @@
           <t>2026-07-23 11:10:52</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -839,6 +875,8 @@
           <t>2026-07-23 11:27:12</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -867,6 +905,8 @@
           <t>2026-07-23 11:51:48</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -895,6 +935,8 @@
           <t>2026-07-23 11:52:39</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -923,6 +965,8 @@
           <t>2026-07-23 11:53:10</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -951,6 +995,8 @@
           <t>2026-07-23 11:53:39</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -979,6 +1025,8 @@
           <t>2026-07-23 12:03:44</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1007,6 +1055,8 @@
           <t>2026-07-23 12:08:27</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1031,6 +1081,8 @@
           <t>2026-07-23 20:27:07</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1059,6 +1111,8 @@
           <t>2026-07-24 10:31:25</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1087,6 +1141,8 @@
           <t>2026-07-24 10:36:32</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1115,6 +1171,8 @@
           <t>2026-07-24 10:53:18</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1143,6 +1201,8 @@
           <t>2026-07-24 12:03:19</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1167,6 +1227,8 @@
           <t>2026-07-24 18:54:03</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1195,6 +1257,8 @@
           <t>2026-07-24 19:21:20</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1223,6 +1287,8 @@
           <t>2026-07-24 20:08:20</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1251,6 +1317,8 @@
           <t>2026-07-24 20:08:57</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1279,6 +1347,8 @@
           <t>2026-07-24 20:09:40</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1307,6 +1377,8 @@
           <t>2026-07-24 20:12:45</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1335,6 +1407,8 @@
           <t>2026-07-24 20:13:02</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1363,6 +1437,8 @@
           <t>2026-07-24 20:13:58</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1391,6 +1467,8 @@
           <t>2026-07-24 20:21:43</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1419,6 +1497,8 @@
           <t>2026-07-24 20:24:55</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1447,6 +1527,8 @@
           <t>2026-07-24 20:32:44</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1475,6 +1557,8 @@
           <t>2026-07-24 20:34:36</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1503,6 +1587,8 @@
           <t>2026-07-24 20:34:46</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1531,6 +1617,553 @@
           <t>2026-07-24 20:42:03</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>25</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-27 10:54:01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>25</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Common Cold</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:59:43</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>25</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:07:30</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Akash </t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>25</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Common Cold</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-02 20:59:14</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dr. Kumar</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eye pain
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Akash </t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>25</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-02 20:59:44</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dr. Kumar</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>25</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-02 21:48:40</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>25</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-02 21:50:37</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>25</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:04:54</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>25</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:28:02</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>25</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:31:09</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>25</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:55:08</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>25</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-02 23:11:49</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>25</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-02 23:15:51</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>nive</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>25</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Migraine</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:34:22</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>25</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Migraine</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:55:43</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Akash</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>25</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-04 23:28:04</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dr. Priya</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
